--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/BlankPivotTableField/BlankPivotTableField.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/BlankPivotTableField/BlankPivotTableField.xlsx
@@ -142,24 +142,26 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="6">
-    <pivotField name="Name" axis="axisCol" showAll="0" defaultSubtotal="0">
-      <items count="5">
+    <pivotField name="Name" axis="axisCol" showAll="0">
+      <items count="6">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField name="Month" axis="axisRow" showAll="0" defaultSubtotal="0">
-      <items count="1">
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField name="Month" axis="axisRow" showAll="0">
+      <items count="2">
         <item x="0"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="4"/>
@@ -183,24 +185,26 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="6">
-    <pivotField name="Name" axis="axisRow" showAll="0" defaultSubtotal="0">
-      <items count="5">
+    <pivotField name="Name" axis="axisRow" showAll="0">
+      <items count="6">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField name="Month" axis="axisCol" showAll="0" defaultSubtotal="0">
-      <items count="1">
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField name="Month" axis="axisCol" showAll="0">
+      <items count="2">
         <item x="0"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="0"/>
@@ -224,24 +228,26 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="6">
-    <pivotField name="Name" axis="axisRow" showAll="0" defaultSubtotal="0">
-      <items count="5">
+    <pivotField name="Name" axis="axisRow" showAll="0">
+      <items count="6">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField name="Month" axis="axisRow" showAll="0" defaultSubtotal="0">
-      <items count="1">
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField name="Month" axis="axisRow" showAll="0">
+      <items count="2">
         <item x="0"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="0"/>
@@ -263,24 +269,26 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="6">
-    <pivotField name="Name" axis="axisCol" showAll="0" defaultSubtotal="0">
-      <items count="5">
+    <pivotField name="Name" axis="axisCol" showAll="0">
+      <items count="6">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField name="Month" axis="axisCol" showAll="0" defaultSubtotal="0">
-      <items count="1">
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField name="Month" axis="axisCol" showAll="0">
+      <items count="2">
         <item x="0"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <colFields count="2">
     <field x="0"/>
@@ -302,21 +310,22 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="6">
-    <pivotField name="Name" axis="axisCol" showAll="0" defaultSubtotal="0">
-      <items count="5">
+    <pivotField name="Name" axis="axisCol" showAll="0">
+      <items count="6">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField name="BakeDate" axis="axisRow" showAll="0" defaultSubtotal="0">
-      <items count="15">
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField name="BakeDate" axis="axisRow" showAll="0">
+      <items count="16">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -332,6 +341,7 @@
         <item x="12"/>
         <item x="13"/>
         <item x="14"/>
+        <item t="default"/>
       </items>
     </pivotField>
   </pivotFields>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/BlankPivotTableField/BlankPivotTableField.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/BlankPivotTableField/BlankPivotTableField.xlsx
@@ -669,12 +669,12 @@
   <x:dimension ref="A1:F17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.853482" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="7.710625" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="18.710625" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="9.710625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9.567768" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11.710625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="9.139196" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:6">

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/BlankPivotTableField/BlankPivotTableField.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/BlankPivotTableField/BlankPivotTableField.xlsx
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="6">
     <pivotField name="Name" axis="axisCol" showAll="0">
@@ -182,7 +182,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="6">
     <pivotField name="Name" axis="axisRow" showAll="0">
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="6">
     <pivotField name="Name" axis="axisRow" showAll="0">
@@ -266,7 +266,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="6">
     <pivotField name="Name" axis="axisCol" showAll="0">
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pvt5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="6">
     <pivotField name="Name" axis="axisCol" showAll="0">
